--- a/resources/school/school.xlsx
+++ b/resources/school/school.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="708" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="CONFIG" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="School" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONFIG" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="School" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="Z_013C542B_6F19_4C79_B0E1_CF7C44EAF100_.wvu.Cols" localSheetId="1" hidden="1">School!#REF!</definedName>
@@ -922,7 +922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="16.75" customWidth="1" style="9" min="1" max="1"/>
@@ -1498,6 +1498,36 @@
         <v>8009</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>太虚剑宗</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="11" t="n">
+        <v>1029</v>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>1075</v>
+      </c>
+      <c r="G13" s="11" t="n">
+        <v>8015</v>
+      </c>
+      <c r="H13" s="11" t="n"/>
+      <c r="I13" s="11" t="n"/>
+      <c r="J13" s="11" t="n"/>
+      <c r="K13" s="11" t="n"/>
+      <c r="L13" s="11" t="n"/>
+      <c r="M13" s="11" t="n"/>
+      <c r="N13" s="11" t="n"/>
+      <c r="O13" s="11" t="n"/>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A4 A13:A1048576">
     <cfRule type="duplicateValues" priority="1966" dxfId="0"/>

--- a/resources/school/school.xlsx
+++ b/resources/school/school.xlsx
@@ -922,7 +922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="16.75" customWidth="1" style="9" min="1" max="1"/>
@@ -1528,6 +1528,38 @@
       <c r="N13" s="11" t="n"/>
       <c r="O13" s="11" t="n"/>
     </row>
+    <row r="14">
+      <c r="A14" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>焚天门</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E14" s="11" t="n">
+        <v>1028</v>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>1090</v>
+      </c>
+      <c r="G14" s="11" t="n">
+        <v>9001</v>
+      </c>
+      <c r="H14" s="11" t="n">
+        <v>9002</v>
+      </c>
+      <c r="I14" s="11" t="n"/>
+      <c r="J14" s="11" t="n"/>
+      <c r="K14" s="11" t="n"/>
+      <c r="L14" s="11" t="n"/>
+      <c r="M14" s="11" t="n"/>
+      <c r="N14" s="11" t="n"/>
+      <c r="O14" s="11" t="n"/>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A4 A13:A1048576">
     <cfRule type="duplicateValues" priority="1966" dxfId="0"/>

--- a/resources/school/school.xlsx
+++ b/resources/school/school.xlsx
@@ -1,13 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\round_dev\workspace_dev\GameConfig\data_table\normal\school\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="708" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="708" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONFIG" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="School" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="CONFIG" sheetId="1" r:id="rId1"/>
+    <sheet name="School" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="Z_013C542B_6F19_4C79_B0E1_CF7C44EAF100_.wvu.Cols" localSheetId="1" hidden="1">School!#REF!</definedName>
@@ -233,85 +239,248 @@
     <definedName name="Z_FAF1ADB8_46A9_40B0_AA1B_9C75E39038F2_.wvu.FilterData" localSheetId="1" hidden="1">School!$A$1:$C$6</definedName>
     <definedName name="Z_FF6A625A_6008_4A1D_8FF0_F8A30B9F02A0_.wvu.FilterData" localSheetId="1" hidden="1">School!$A$1:$C$6</definedName>
   </definedNames>
-  <calcPr calcId="162913" fullCalcOnLoad="1"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="42">
+  <si>
+    <t>表名</t>
+  </si>
+  <si>
+    <t>说明</t>
+  </si>
+  <si>
+    <t>列作用说明</t>
+  </si>
+  <si>
+    <t>生成文件</t>
+  </si>
+  <si>
+    <t>填表说明</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>名称</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>门派</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>导出目标</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>需要导出的sheet</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>导出文件</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>SERVER</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>CLIENT</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>_desc:string</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>school:int</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>name:string</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>神通id</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>school_ability_id[0]:int</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>school_ability_id[1]:int</t>
+  </si>
+  <si>
+    <t>school_ability_id[2]:int</t>
+  </si>
+  <si>
+    <t>school_ability_id[3]:int</t>
+  </si>
+  <si>
+    <t>school_ability_id[4]:int</t>
+  </si>
+  <si>
+    <t>school_ability_id[5]:int</t>
+  </si>
+  <si>
+    <t>school_ability_id[6]:int</t>
+  </si>
+  <si>
+    <t>school_ability_id[7]:int</t>
+  </si>
+  <si>
+    <t>school_ability_id[8]:int</t>
+  </si>
+  <si>
+    <t>school/school_data.py</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>School</t>
+  </si>
+  <si>
+    <t>人物门派配置</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>门派类型
+1：物理
+2：法术
+3：治疗
+4：封印</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>school_type:int</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>剑修</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>风法</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>水奶</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>符箓</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>枪修</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>火法</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>木奶</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>妖术</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>model_id:int</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>战斗model_id</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>大世界model_id</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>combat_model_id:int</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color indexed="8"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <color indexed="8"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color indexed="8"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
-      <family val="2"/>
-      <color indexed="8"/>
-      <sz val="10"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <family val="3"/>
-      <color indexed="8"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="12"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <family val="3"/>
-      <sz val="12"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <family val="3"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <family val="3"/>
-      <color indexed="8"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color indexed="8"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
-      <family val="2"/>
-      <color indexed="8"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <family val="3"/>
-      <sz val="9"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FFD19A66"/>
       <name val="Consolas"/>
       <family val="3"/>
-      <color rgb="FFD19A66"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.5999938962981048"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -347,99 +516,99 @@
     </border>
   </borders>
   <cellStyleXfs count="12">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="17">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="9" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="9" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="9"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="9"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="8" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="9" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="9" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="9" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="9" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="12">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 6" xfId="1"/>
+    <cellStyle name="常规 11" xfId="11"/>
+    <cellStyle name="常规 2" xfId="4"/>
     <cellStyle name="常规 2 2" xfId="2"/>
     <cellStyle name="常规 2 3" xfId="3"/>
-    <cellStyle name="常规 2" xfId="4"/>
     <cellStyle name="常规 3" xfId="5"/>
     <cellStyle name="常规 4" xfId="6"/>
     <cellStyle name="常规 5" xfId="7"/>
+    <cellStyle name="常规 6" xfId="1"/>
+    <cellStyle name="常规 7" xfId="10"/>
     <cellStyle name="常规_CONFIG" xfId="8"/>
     <cellStyle name="常规_Sheet1" xfId="9"/>
-    <cellStyle name="常规 7" xfId="10"/>
-    <cellStyle name="常规 11" xfId="11"/>
   </cellStyles>
   <dxfs count="3">
     <dxf>
@@ -474,74 +643,14 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -802,775 +911,599 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H5"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col width="21.125" customWidth="1" style="8" min="1" max="1"/>
-    <col width="13.875" bestFit="1" customWidth="1" style="8" min="2" max="2"/>
-    <col width="49.5" customWidth="1" style="8" min="3" max="3"/>
-    <col width="30.125" customWidth="1" style="8" min="4" max="4"/>
-    <col width="23.5" customWidth="1" style="8" min="5" max="5"/>
-    <col width="19.25" customWidth="1" style="8" min="6" max="6"/>
-    <col width="21.375" customWidth="1" style="8" min="8" max="8"/>
+    <col min="1" max="1" width="21.125" style="8" customWidth="1"/>
+    <col min="2" max="2" width="13.875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="49.5" style="8" customWidth="1"/>
+    <col min="4" max="4" width="30.125" style="8" customWidth="1"/>
+    <col min="5" max="5" width="23.5" style="8" customWidth="1"/>
+    <col min="6" max="6" width="19.25" style="8" customWidth="1"/>
+    <col min="8" max="8" width="21.375" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1" s="8">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>表名</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>人物门派配置</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="n"/>
-    </row>
-    <row r="2" ht="15.75" customHeight="1" s="8">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>说明</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="n"/>
-      <c r="C2" s="4" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-    </row>
-    <row r="3" ht="16.5" customHeight="1" s="8">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>列作用说明</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>导出目标</t>
-        </is>
-      </c>
-      <c r="C3" s="7" t="inlineStr">
-        <is>
-          <t>需要导出的sheet</t>
-        </is>
-      </c>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>导出文件</t>
-        </is>
-      </c>
-      <c r="E3" s="0" t="n"/>
-      <c r="F3" s="0" t="n"/>
-      <c r="H3" s="0" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>生成文件</t>
-        </is>
-      </c>
-      <c r="B4" s="0" t="inlineStr">
-        <is>
-          <t>SERVER</t>
-        </is>
-      </c>
-      <c r="C4" s="14" t="inlineStr">
-        <is>
-          <t>School</t>
-        </is>
-      </c>
-      <c r="D4" s="14" t="inlineStr">
-        <is>
-          <t>school/school_data.py</t>
-        </is>
-      </c>
-      <c r="E4" s="0" t="n"/>
-    </row>
-    <row r="5">
-      <c r="B5" s="0" t="inlineStr">
-        <is>
-          <t>CLIENT</t>
-        </is>
-      </c>
-      <c r="C5" s="14" t="inlineStr">
-        <is>
-          <t>School</t>
-        </is>
-      </c>
-      <c r="D5" s="14" t="inlineStr">
-        <is>
-          <t>school/school_data.py</t>
-        </is>
+    <row r="1" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="4"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="4"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+    </row>
+    <row r="3" spans="1:8" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A3" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3"/>
+      <c r="F3"/>
+      <c r="H3"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="B5" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:O14"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:O12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col width="16.75" customWidth="1" style="9" min="1" max="1"/>
-    <col width="21.875" customWidth="1" style="9" min="2" max="2"/>
-    <col width="20" customWidth="1" style="9" min="3" max="4"/>
-    <col width="19" customWidth="1" style="9" min="5" max="7"/>
-    <col width="19" customWidth="1" style="13" min="8" max="15"/>
-    <col width="9" customWidth="1" style="13" min="16" max="16384"/>
+    <col min="1" max="1" width="16.75" style="9" customWidth="1"/>
+    <col min="2" max="2" width="21.875" style="9" customWidth="1"/>
+    <col min="3" max="4" width="20" style="9" customWidth="1"/>
+    <col min="5" max="7" width="19" style="9" customWidth="1"/>
+    <col min="8" max="15" width="19" style="13" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="94.5" customFormat="1" customHeight="1" s="1">
-      <c r="A1" s="10" t="inlineStr">
-        <is>
-          <t>门派</t>
-        </is>
-      </c>
-      <c r="B1" s="10" t="inlineStr">
-        <is>
-          <t>填表说明</t>
-        </is>
-      </c>
-      <c r="C1" s="10" t="inlineStr">
-        <is>
-          <t>名称</t>
-        </is>
-      </c>
-      <c r="D1" s="10" t="inlineStr">
-        <is>
-          <t>门派类型
-1：物理
-2：法术
-3：治疗
-4：封印</t>
-        </is>
-      </c>
-      <c r="E1" s="10" t="inlineStr">
-        <is>
-          <t>大世界model_id</t>
-        </is>
-      </c>
-      <c r="F1" s="10" t="inlineStr">
-        <is>
-          <t>战斗model_id</t>
-        </is>
-      </c>
-      <c r="G1" s="10" t="inlineStr">
-        <is>
-          <t>神通id</t>
-        </is>
-      </c>
-      <c r="H1" s="10" t="inlineStr">
-        <is>
-          <t>神通id</t>
-        </is>
-      </c>
-      <c r="I1" s="10" t="inlineStr">
-        <is>
-          <t>神通id</t>
-        </is>
-      </c>
-      <c r="J1" s="10" t="inlineStr">
-        <is>
-          <t>神通id</t>
-        </is>
-      </c>
-      <c r="K1" s="10" t="inlineStr">
-        <is>
-          <t>神通id</t>
-        </is>
-      </c>
-      <c r="L1" s="10" t="inlineStr">
-        <is>
-          <t>神通id</t>
-        </is>
-      </c>
-      <c r="M1" s="10" t="inlineStr">
-        <is>
-          <t>神通id</t>
-        </is>
-      </c>
-      <c r="N1" s="10" t="inlineStr">
-        <is>
-          <t>神通id</t>
-        </is>
-      </c>
-      <c r="O1" s="10" t="inlineStr">
-        <is>
-          <t>神通id</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="36.75" customFormat="1" customHeight="1" s="15">
-      <c r="A2" s="12" t="inlineStr">
-        <is>
-          <t>school:int</t>
-        </is>
-      </c>
-      <c r="B2" s="12" t="inlineStr">
-        <is>
-          <t>_desc:string</t>
-        </is>
-      </c>
-      <c r="C2" s="12" t="inlineStr">
-        <is>
-          <t>name:string</t>
-        </is>
-      </c>
-      <c r="D2" s="12" t="inlineStr">
-        <is>
-          <t>school_type:int</t>
-        </is>
-      </c>
-      <c r="E2" s="12" t="inlineStr">
-        <is>
-          <t>model_id:int</t>
-        </is>
-      </c>
-      <c r="F2" s="12" t="inlineStr">
-        <is>
-          <t>combat_model_id:int</t>
-        </is>
-      </c>
-      <c r="G2" s="12" t="inlineStr">
-        <is>
-          <t>school_ability_id[0]:int</t>
-        </is>
-      </c>
-      <c r="H2" s="12" t="inlineStr">
-        <is>
-          <t>school_ability_id[1]:int</t>
-        </is>
-      </c>
-      <c r="I2" s="12" t="inlineStr">
-        <is>
-          <t>school_ability_id[2]:int</t>
-        </is>
-      </c>
-      <c r="J2" s="12" t="inlineStr">
-        <is>
-          <t>school_ability_id[3]:int</t>
-        </is>
-      </c>
-      <c r="K2" s="12" t="inlineStr">
-        <is>
-          <t>school_ability_id[4]:int</t>
-        </is>
-      </c>
-      <c r="L2" s="12" t="inlineStr">
-        <is>
-          <t>school_ability_id[5]:int</t>
-        </is>
-      </c>
-      <c r="M2" s="12" t="inlineStr">
-        <is>
-          <t>school_ability_id[6]:int</t>
-        </is>
-      </c>
-      <c r="N2" s="12" t="inlineStr">
-        <is>
-          <t>school_ability_id[7]:int</t>
-        </is>
-      </c>
-      <c r="O2" s="12" t="inlineStr">
-        <is>
-          <t>school_ability_id[8]:int</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="16.5" customFormat="1" customHeight="1" s="1">
-      <c r="A3" s="10" t="n"/>
-      <c r="B3" s="10" t="n"/>
-      <c r="C3" s="10" t="n"/>
-      <c r="D3" s="10" t="n"/>
-      <c r="E3" s="10" t="n"/>
-      <c r="F3" s="10" t="n"/>
-      <c r="G3" s="10" t="n"/>
-      <c r="H3" s="10" t="n"/>
-      <c r="I3" s="10" t="n"/>
-      <c r="J3" s="10" t="n"/>
-      <c r="K3" s="10" t="n"/>
-      <c r="L3" s="10" t="n"/>
-      <c r="M3" s="10" t="n"/>
-      <c r="N3" s="10" t="n"/>
-      <c r="O3" s="10" t="n"/>
-    </row>
-    <row r="4" ht="16.5" customFormat="1" customHeight="1" s="1">
-      <c r="A4" s="10" t="n"/>
-      <c r="B4" s="10" t="n"/>
-      <c r="C4" s="10" t="n"/>
-      <c r="D4" s="10" t="n"/>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="10" t="n"/>
-      <c r="G4" s="10" t="n"/>
-      <c r="H4" s="10" t="n"/>
-      <c r="I4" s="10" t="n"/>
-      <c r="J4" s="10" t="n"/>
-      <c r="K4" s="10" t="n"/>
-      <c r="L4" s="10" t="n"/>
-      <c r="M4" s="10" t="n"/>
-      <c r="N4" s="10" t="n"/>
-      <c r="O4" s="10" t="n"/>
-    </row>
-    <row r="5" ht="16.5" customHeight="1" s="8">
-      <c r="A5" s="16" t="n">
+    <row r="1" spans="1:15" s="1" customFormat="1" ht="94.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="N1" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="O1" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" s="15" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="N2" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="O2" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+    </row>
+    <row r="4" spans="1:15" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+    </row>
+    <row r="5" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="16">
         <v>1</v>
       </c>
-      <c r="B5" s="11" t="n"/>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>剑修</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="n">
+      <c r="B5" s="11"/>
+      <c r="C5" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="11">
         <v>1</v>
       </c>
-      <c r="E5" s="11" t="n">
+      <c r="E5" s="11">
         <v>1027</v>
       </c>
-      <c r="F5" s="11" t="n">
+      <c r="F5" s="11">
         <v>1074</v>
       </c>
-      <c r="G5" s="11" t="n">
+      <c r="G5" s="11">
         <v>1001</v>
       </c>
-      <c r="H5" s="11" t="n">
+      <c r="H5" s="11">
         <v>1002</v>
       </c>
-      <c r="I5" s="11" t="n">
+      <c r="I5" s="11">
         <v>1003</v>
       </c>
-      <c r="J5" s="11" t="n">
+      <c r="J5" s="11">
         <v>1004</v>
       </c>
-      <c r="K5" s="11" t="n">
+      <c r="K5" s="11">
         <v>1005</v>
       </c>
-      <c r="L5" s="11" t="n">
+      <c r="L5" s="11">
         <v>1006</v>
       </c>
-      <c r="M5" s="11" t="n">
+      <c r="M5" s="11">
         <v>1007</v>
       </c>
-      <c r="N5" s="11" t="n">
+      <c r="N5" s="11">
         <v>1008</v>
       </c>
-      <c r="O5" s="11" t="n">
+      <c r="O5" s="11">
         <v>1009</v>
       </c>
     </row>
-    <row r="6" ht="16.5" customHeight="1" s="8">
-      <c r="A6" s="16" t="n">
+    <row r="6" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="16">
         <v>2</v>
       </c>
-      <c r="B6" s="11" t="n"/>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>风法</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="n">
+      <c r="B6" s="11"/>
+      <c r="C6" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="11">
         <v>2</v>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="E6" s="11">
         <v>1027</v>
       </c>
-      <c r="F6" s="11" t="n">
+      <c r="F6" s="11">
         <v>1067</v>
       </c>
-      <c r="G6" s="11" t="n">
+      <c r="G6" s="11">
         <v>2001</v>
       </c>
-      <c r="H6" s="11" t="n">
+      <c r="H6" s="11">
         <v>2002</v>
       </c>
-      <c r="I6" s="11" t="n">
+      <c r="I6" s="11">
         <v>2003</v>
       </c>
-      <c r="J6" s="11" t="n">
+      <c r="J6" s="11">
         <v>2004</v>
       </c>
-      <c r="K6" s="11" t="n">
+      <c r="K6" s="11">
         <v>2005</v>
       </c>
-      <c r="L6" s="11" t="n">
+      <c r="L6" s="11">
         <v>2006</v>
       </c>
-      <c r="M6" s="11" t="n">
+      <c r="M6" s="11">
         <v>2007</v>
       </c>
-      <c r="N6" s="11" t="n">
+      <c r="N6" s="11">
         <v>2008</v>
       </c>
-      <c r="O6" s="11" t="n">
+      <c r="O6" s="11">
         <v>2009</v>
       </c>
     </row>
-    <row r="7" ht="16.5" customHeight="1" s="8">
-      <c r="A7" s="16" t="n">
+    <row r="7" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="16">
         <v>3</v>
       </c>
-      <c r="B7" s="11" t="n"/>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>水奶</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="n">
+      <c r="B7" s="11"/>
+      <c r="C7" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="11">
         <v>3</v>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E7" s="11">
         <v>1027</v>
       </c>
-      <c r="F7" s="11" t="n">
+      <c r="F7" s="11">
         <v>1070</v>
       </c>
-      <c r="G7" s="11" t="n">
+      <c r="G7" s="11">
         <v>3001</v>
       </c>
-      <c r="H7" s="11" t="n">
+      <c r="H7" s="11">
         <v>3002</v>
       </c>
-      <c r="I7" s="11" t="n">
+      <c r="I7" s="11">
         <v>3003</v>
       </c>
-      <c r="J7" s="11" t="n">
+      <c r="J7" s="11">
         <v>3004</v>
       </c>
-      <c r="K7" s="11" t="n">
+      <c r="K7" s="11">
         <v>3005</v>
       </c>
-      <c r="L7" s="11" t="n">
+      <c r="L7" s="11">
         <v>3006</v>
       </c>
-      <c r="M7" s="11" t="n">
+      <c r="M7" s="11">
         <v>3007</v>
       </c>
-      <c r="N7" s="11" t="n">
+      <c r="N7" s="11">
         <v>3008</v>
       </c>
-      <c r="O7" s="11" t="n">
+      <c r="O7" s="11">
         <v>3009</v>
       </c>
     </row>
-    <row r="8" ht="16.5" customHeight="1" s="8">
-      <c r="A8" s="16" t="n">
+    <row r="8" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="16">
         <v>4</v>
       </c>
-      <c r="B8" s="11" t="n"/>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>符箓</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="n">
+      <c r="B8" s="11"/>
+      <c r="C8" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="11">
         <v>4</v>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="11">
         <v>1027</v>
       </c>
-      <c r="F8" s="11" t="n">
+      <c r="F8" s="11">
         <v>1068</v>
       </c>
-      <c r="G8" s="11" t="n">
+      <c r="G8" s="11">
         <v>4001</v>
       </c>
-      <c r="H8" s="11" t="n">
+      <c r="H8" s="11">
         <v>4002</v>
       </c>
-      <c r="I8" s="11" t="n">
+      <c r="I8" s="11">
         <v>4003</v>
       </c>
-      <c r="J8" s="11" t="n">
+      <c r="J8" s="11">
         <v>4004</v>
       </c>
-      <c r="K8" s="11" t="n">
+      <c r="K8" s="11">
         <v>4005</v>
       </c>
-      <c r="L8" s="11" t="n">
+      <c r="L8" s="11">
         <v>4006</v>
       </c>
-      <c r="M8" s="11" t="n">
+      <c r="M8" s="11">
         <v>4007</v>
       </c>
-      <c r="N8" s="11" t="n">
+      <c r="N8" s="11">
         <v>4008</v>
       </c>
-      <c r="O8" s="11" t="n">
+      <c r="O8" s="11">
         <v>4009</v>
       </c>
     </row>
-    <row r="9" ht="16.5" customHeight="1" s="8">
-      <c r="A9" s="16" t="n">
+    <row r="9" spans="1:15" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A9" s="16">
         <v>5</v>
       </c>
-      <c r="B9" s="11" t="n"/>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>枪修</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="n">
+      <c r="B9" s="11"/>
+      <c r="C9" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="11">
         <v>1</v>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="E9" s="11">
         <v>1027</v>
       </c>
-      <c r="F9" s="11" t="n">
+      <c r="F9" s="11">
         <v>1074</v>
       </c>
-      <c r="G9" s="11" t="n">
+      <c r="G9" s="11">
         <v>5001</v>
       </c>
-      <c r="H9" s="11" t="n">
+      <c r="H9" s="11">
         <v>5002</v>
       </c>
-      <c r="I9" s="11" t="n">
+      <c r="I9" s="11">
         <v>5003</v>
       </c>
-      <c r="J9" s="11" t="n">
+      <c r="J9" s="11">
         <v>5004</v>
       </c>
-      <c r="K9" s="11" t="n">
+      <c r="K9" s="11">
         <v>5005</v>
       </c>
-      <c r="L9" s="11" t="n">
+      <c r="L9" s="11">
         <v>5006</v>
       </c>
-      <c r="M9" s="11" t="n">
+      <c r="M9" s="11">
         <v>5007</v>
       </c>
-      <c r="N9" s="11" t="n">
+      <c r="N9" s="11">
         <v>5008</v>
       </c>
-      <c r="O9" s="11" t="n">
+      <c r="O9" s="11">
         <v>5009</v>
       </c>
     </row>
-    <row r="10" ht="16.5" customHeight="1" s="8">
-      <c r="A10" s="16" t="n">
+    <row r="10" spans="1:15" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A10" s="16">
         <v>6</v>
       </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>火法</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="n">
+      <c r="C10" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="9">
         <v>2</v>
       </c>
-      <c r="E10" s="11" t="n">
-        <v>1028</v>
-      </c>
-      <c r="F10" s="11" t="n">
+      <c r="E10" s="11">
+        <v>1027</v>
+      </c>
+      <c r="F10" s="11">
+        <v>1067</v>
+      </c>
+      <c r="G10" s="11">
+        <v>6001</v>
+      </c>
+      <c r="H10" s="11">
+        <v>6002</v>
+      </c>
+      <c r="I10" s="11">
+        <v>6003</v>
+      </c>
+      <c r="J10" s="11">
+        <v>6004</v>
+      </c>
+      <c r="K10" s="11">
+        <v>6005</v>
+      </c>
+      <c r="L10" s="11">
+        <v>6006</v>
+      </c>
+      <c r="M10" s="11">
+        <v>6007</v>
+      </c>
+      <c r="N10" s="11">
+        <v>6008</v>
+      </c>
+      <c r="O10" s="11">
+        <v>6009</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A11" s="16">
+        <v>7</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="9">
+        <v>3</v>
+      </c>
+      <c r="E11" s="11">
+        <v>1027</v>
+      </c>
+      <c r="F11" s="11">
+        <v>1070</v>
+      </c>
+      <c r="G11" s="11">
+        <v>7001</v>
+      </c>
+      <c r="H11" s="11">
+        <v>7002</v>
+      </c>
+      <c r="I11" s="11">
+        <v>7003</v>
+      </c>
+      <c r="J11" s="11">
+        <v>7004</v>
+      </c>
+      <c r="K11" s="11">
+        <v>7005</v>
+      </c>
+      <c r="L11" s="11">
+        <v>7006</v>
+      </c>
+      <c r="M11" s="11">
+        <v>7007</v>
+      </c>
+      <c r="N11" s="11">
+        <v>7008</v>
+      </c>
+      <c r="O11" s="11">
+        <v>7009</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A12" s="16">
+        <v>8</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" s="9">
+        <v>4</v>
+      </c>
+      <c r="E12" s="11">
+        <v>1027</v>
+      </c>
+      <c r="F12" s="11">
         <v>1068</v>
       </c>
-      <c r="G10" s="11" t="n">
-        <v>6001</v>
-      </c>
-      <c r="H10" s="11" t="n">
-        <v>6002</v>
-      </c>
-      <c r="I10" s="11" t="n">
-        <v>6003</v>
-      </c>
-      <c r="J10" s="11" t="n">
-        <v>6004</v>
-      </c>
-      <c r="K10" s="11" t="n">
-        <v>6005</v>
-      </c>
-      <c r="L10" s="11" t="n">
-        <v>6006</v>
-      </c>
-      <c r="M10" s="11" t="n">
-        <v>6007</v>
-      </c>
-      <c r="N10" s="11" t="n">
-        <v>6008</v>
-      </c>
-      <c r="O10" s="11" t="n">
-        <v>6009</v>
-      </c>
-    </row>
-    <row r="11" ht="16.5" customHeight="1" s="8">
-      <c r="A11" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>木奶</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="E11" s="11" t="n">
-        <v>1027</v>
-      </c>
-      <c r="F11" s="11" t="n">
-        <v>1070</v>
-      </c>
-      <c r="G11" s="11" t="n">
-        <v>7001</v>
-      </c>
-      <c r="H11" s="11" t="n">
-        <v>7002</v>
-      </c>
-      <c r="I11" s="11" t="n">
-        <v>7003</v>
-      </c>
-      <c r="J11" s="11" t="n">
-        <v>7004</v>
-      </c>
-      <c r="K11" s="11" t="n">
-        <v>7005</v>
-      </c>
-      <c r="L11" s="11" t="n">
-        <v>7006</v>
-      </c>
-      <c r="M11" s="11" t="n">
-        <v>7007</v>
-      </c>
-      <c r="N11" s="11" t="n">
-        <v>7008</v>
-      </c>
-      <c r="O11" s="11" t="n">
-        <v>7009</v>
-      </c>
-    </row>
-    <row r="12" ht="16.5" customHeight="1" s="8">
-      <c r="A12" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>妖术</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="E12" s="11" t="n">
-        <v>1027</v>
-      </c>
-      <c r="F12" s="11" t="n">
-        <v>1068</v>
-      </c>
-      <c r="G12" s="11" t="n">
+      <c r="G12" s="11">
         <v>8001</v>
       </c>
-      <c r="H12" s="11" t="n">
+      <c r="H12" s="11">
         <v>8002</v>
       </c>
-      <c r="I12" s="11" t="n">
+      <c r="I12" s="11">
         <v>8003</v>
       </c>
-      <c r="J12" s="11" t="n">
+      <c r="J12" s="11">
         <v>8004</v>
       </c>
-      <c r="K12" s="11" t="n">
+      <c r="K12" s="11">
         <v>8005</v>
       </c>
-      <c r="L12" s="11" t="n">
+      <c r="L12" s="11">
         <v>8006</v>
       </c>
-      <c r="M12" s="11" t="n">
+      <c r="M12" s="11">
         <v>8007</v>
       </c>
-      <c r="N12" s="11" t="n">
+      <c r="N12" s="11">
         <v>8008</v>
       </c>
-      <c r="O12" s="11" t="n">
+      <c r="O12" s="11">
         <v>8009</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="16" t="n">
-        <v>9</v>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>太虚剑宗</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="11" t="n">
-        <v>1029</v>
-      </c>
-      <c r="F13" s="11" t="n">
-        <v>1075</v>
-      </c>
-      <c r="G13" s="11" t="n">
-        <v>8015</v>
-      </c>
-      <c r="H13" s="11" t="n"/>
-      <c r="I13" s="11" t="n"/>
-      <c r="J13" s="11" t="n"/>
-      <c r="K13" s="11" t="n"/>
-      <c r="L13" s="11" t="n"/>
-      <c r="M13" s="11" t="n"/>
-      <c r="N13" s="11" t="n"/>
-      <c r="O13" s="11" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>焚天门</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="E14" s="11" t="n">
-        <v>1028</v>
-      </c>
-      <c r="F14" s="11" t="n">
-        <v>1090</v>
-      </c>
-      <c r="G14" s="11" t="n">
-        <v>9001</v>
-      </c>
-      <c r="H14" s="11" t="n">
-        <v>9002</v>
-      </c>
-      <c r="I14" s="11" t="n"/>
-      <c r="J14" s="11" t="n"/>
-      <c r="K14" s="11" t="n"/>
-      <c r="L14" s="11" t="n"/>
-      <c r="M14" s="11" t="n"/>
-      <c r="N14" s="11" t="n"/>
-      <c r="O14" s="11" t="n"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:A4 A13:A1048576">
-    <cfRule type="duplicateValues" priority="1966" dxfId="0"/>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <conditionalFormatting sqref="A13:A1048576 A1:A4">
+    <cfRule type="duplicateValues" dxfId="2" priority="1966"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:E2 G2:O2">
-    <cfRule type="duplicateValues" priority="1968" dxfId="0"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1968"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2">
-    <cfRule type="duplicateValues" priority="1" dxfId="0"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>